--- a/public/assets/excel/employee_general_info.xlsx
+++ b/public/assets/excel/employee_general_info.xlsx
@@ -1,40 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo LOQ\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244A19EB-ECFE-45E7-B142-19922ACF2943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95BAE4A1-D4B9-4653-B822-36B59C7CEC27}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="103">
   <si>
     <t>Applicant_id</t>
   </si>
@@ -48,10 +29,13 @@
     <t>First Name</t>
   </si>
   <si>
+    <t>Middle Name</t>
+  </si>
+  <si>
     <t>Last Name</t>
   </si>
   <si>
-    <t>Middle Name</t>
+    <t>Full name</t>
   </si>
   <si>
     <t>Father Name</t>
@@ -63,9 +47,6 @@
     <t>Spouse Name</t>
   </si>
   <si>
-    <t>Full name</t>
-  </si>
-  <si>
     <t>Marital Status</t>
   </si>
   <si>
@@ -78,6 +59,9 @@
     <t>Nationality</t>
   </si>
   <si>
+    <t>Blood Group</t>
+  </si>
+  <si>
     <t>Height(Feet)</t>
   </si>
   <si>
@@ -204,172 +188,187 @@
     <t>Date of Birth</t>
   </si>
   <si>
+    <t>PC4567865</t>
+  </si>
+  <si>
+    <t>Enamul</t>
+  </si>
+  <si>
+    <t>Dhar</t>
+  </si>
+  <si>
+    <t>Karim</t>
+  </si>
+  <si>
+    <t>Enamul Karim Mozumder</t>
+  </si>
+  <si>
+    <t>Abdul Gaffar Khan</t>
+  </si>
+  <si>
+    <t>Nasima Begum</t>
+  </si>
+  <si>
+    <t>Nusrat Jahan</t>
+  </si>
+  <si>
+    <t>Married</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Islam</t>
+  </si>
+  <si>
+    <t>Bangladeshi</t>
+  </si>
+  <si>
+    <t>House #54, Road #8</t>
+  </si>
+  <si>
+    <t>Noakhali</t>
+  </si>
+  <si>
+    <t>Noakhali Sadar</t>
+  </si>
+  <si>
+    <t>Chittagong</t>
+  </si>
+  <si>
+    <t>Chittagong Division</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>Village Kacha, House #10</t>
+  </si>
+  <si>
+    <t>Comilla</t>
+  </si>
+  <si>
+    <t>Comilla Cantonment</t>
+  </si>
+  <si>
+    <t>REF202302</t>
+  </si>
+  <si>
+    <t>Faisal Ahmed</t>
+  </si>
+  <si>
+    <t>Senior Manager</t>
+  </si>
+  <si>
+    <t>faisal.ahmed@abccompany.com</t>
+  </si>
+  <si>
+    <t>123/2, New Colony Road</t>
+  </si>
+  <si>
+    <t>Dhaka</t>
+  </si>
+  <si>
+    <t>Gulshan</t>
+  </si>
+  <si>
+    <t>Dhaka Division</t>
+  </si>
+  <si>
+    <t>A1234567</t>
+  </si>
+  <si>
+    <t>B4567890</t>
+  </si>
+  <si>
+    <t>R123456789</t>
+  </si>
+  <si>
+    <t>rashid.khan@gmail.com</t>
+  </si>
+  <si>
+    <t>rashid.khan@xyzcorp.com</t>
+  </si>
+  <si>
+    <t>2-87654321</t>
+  </si>
+  <si>
+    <t>02-12345678</t>
+  </si>
+  <si>
+    <t>Bhe15454</t>
+  </si>
+  <si>
+    <t>Personal Email</t>
+  </si>
+  <si>
+    <t>Work Email</t>
+  </si>
+  <si>
+    <t>Work Phone</t>
+  </si>
+  <si>
+    <t>Work Mobile</t>
+  </si>
+  <si>
+    <t>Home Phone</t>
+  </si>
+  <si>
+    <t>Personal Mobile</t>
+  </si>
+  <si>
+    <t>Birth Registration No</t>
+  </si>
+  <si>
     <t>Birth Country</t>
   </si>
   <si>
-    <t>Birth Registration No</t>
-  </si>
-  <si>
-    <t>Personal Mobile</t>
-  </si>
-  <si>
-    <t>Home Phone</t>
-  </si>
-  <si>
-    <t>Work Mobile</t>
-  </si>
-  <si>
-    <t>Work Phone</t>
-  </si>
-  <si>
-    <t>Work Email</t>
-  </si>
-  <si>
-    <t>Personal Email</t>
-  </si>
-  <si>
-    <t>Abdul Gaffar Khan</t>
-  </si>
-  <si>
-    <t>Nasima Begum</t>
-  </si>
-  <si>
-    <t>Nusrat Jahan</t>
-  </si>
-  <si>
-    <t>Married</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Islam</t>
-  </si>
-  <si>
-    <t>Bangladeshi</t>
-  </si>
-  <si>
-    <t>House #54, Road #8</t>
-  </si>
-  <si>
-    <t>Noakhali</t>
-  </si>
-  <si>
-    <t>Noakhali Sadar</t>
-  </si>
-  <si>
-    <t>Chittagong</t>
-  </si>
-  <si>
-    <t>Chittagong Division</t>
-  </si>
-  <si>
-    <t>Bangladesh</t>
-  </si>
-  <si>
-    <t>Village Kacha, House #10</t>
-  </si>
-  <si>
-    <t>Comilla</t>
-  </si>
-  <si>
-    <t>Comilla Cantonment</t>
-  </si>
-  <si>
-    <t>REF202302</t>
-  </si>
-  <si>
-    <t>Faisal Ahmed</t>
-  </si>
-  <si>
-    <t>Senior Manager</t>
-  </si>
-  <si>
-    <t>faisal.ahmed@abccompany.com</t>
-  </si>
-  <si>
-    <t>123/2, New Colony Road</t>
-  </si>
-  <si>
-    <t>Dhaka</t>
-  </si>
-  <si>
-    <t>Gulshan</t>
-  </si>
-  <si>
-    <t>Dhaka Division</t>
-  </si>
-  <si>
-    <t>A1234567</t>
-  </si>
-  <si>
-    <t>B4567890</t>
-  </si>
-  <si>
-    <t>R123456789</t>
-  </si>
-  <si>
-    <t>Bhe15454</t>
-  </si>
-  <si>
-    <t>02-12345678</t>
-  </si>
-  <si>
-    <t>2-87654321</t>
-  </si>
-  <si>
-    <t>rashid.khan@xyzcorp.com</t>
-  </si>
-  <si>
-    <t>rashid.khan@gmail.com</t>
-  </si>
-  <si>
-    <t>PC4567865</t>
-  </si>
-  <si>
-    <t>Enamul</t>
-  </si>
-  <si>
-    <t>Karim</t>
-  </si>
-  <si>
-    <t>Enamul Karim Mozumder</t>
-  </si>
-  <si>
-    <t>Dhar</t>
+    <t>NID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos"/>
-      <family val="2"/>
     </font>
     <font>
-      <u/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="single"/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color rgb="FF467886"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -389,34 +388,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="14" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -463,7 +452,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -515,7 +504,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -576,234 +565,244 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED1EF82A-8687-4EDE-9CE4-14A1B2F6C136}">
-  <dimension ref="A1:BL2"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:BN2"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.5" customWidth="1"/>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="5" width="12.09765625" customWidth="1"/>
-    <col min="6" max="6" width="9.8984375" customWidth="1"/>
-    <col min="7" max="7" width="19.19921875" customWidth="1"/>
-    <col min="8" max="8" width="22.59765625" customWidth="1"/>
-    <col min="9" max="9" width="18.3984375" customWidth="1"/>
-    <col min="10" max="10" width="15.8984375" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="13.296875" customWidth="1"/>
-    <col min="13" max="13" width="13.69921875" customWidth="1"/>
-    <col min="14" max="14" width="15.796875" customWidth="1"/>
-    <col min="15" max="15" width="14.69921875" customWidth="1"/>
-    <col min="16" max="17" width="16.5" customWidth="1"/>
-    <col min="18" max="18" width="20.796875" customWidth="1"/>
-    <col min="19" max="19" width="21.09765625" customWidth="1"/>
-    <col min="20" max="20" width="24.5" customWidth="1"/>
-    <col min="21" max="21" width="23.796875" customWidth="1"/>
-    <col min="22" max="22" width="23.19921875" customWidth="1"/>
-    <col min="23" max="24" width="23.69921875" customWidth="1"/>
-    <col min="25" max="25" width="24.296875" customWidth="1"/>
-    <col min="26" max="26" width="24.796875" customWidth="1"/>
-    <col min="27" max="27" width="28.8984375" customWidth="1"/>
-    <col min="28" max="28" width="30.5" customWidth="1"/>
-    <col min="29" max="29" width="26.59765625" customWidth="1"/>
-    <col min="30" max="30" width="26.5" customWidth="1"/>
-    <col min="31" max="31" width="24.3984375" customWidth="1"/>
-    <col min="32" max="32" width="23.5" customWidth="1"/>
-    <col min="33" max="33" width="28.796875" customWidth="1"/>
-    <col min="34" max="34" width="28.5" customWidth="1"/>
-    <col min="35" max="35" width="33.796875" customWidth="1"/>
-    <col min="36" max="36" width="37.59765625" customWidth="1"/>
-    <col min="37" max="37" width="28.796875" customWidth="1"/>
-    <col min="38" max="38" width="25.5" customWidth="1"/>
-    <col min="39" max="39" width="22.3984375" customWidth="1"/>
-    <col min="40" max="40" width="21.796875" customWidth="1"/>
-    <col min="41" max="41" width="21.296875" customWidth="1"/>
-    <col min="42" max="42" width="23.796875" customWidth="1"/>
-    <col min="43" max="43" width="26.5" customWidth="1"/>
-    <col min="44" max="44" width="23.5" customWidth="1"/>
-    <col min="45" max="45" width="25.09765625" customWidth="1"/>
-    <col min="46" max="46" width="24.8984375" customWidth="1"/>
-    <col min="47" max="47" width="24.19921875" customWidth="1"/>
-    <col min="48" max="48" width="23.5" customWidth="1"/>
-    <col min="49" max="49" width="15.296875" customWidth="1"/>
-    <col min="50" max="50" width="18.5" customWidth="1"/>
-    <col min="51" max="51" width="17.796875" customWidth="1"/>
-    <col min="52" max="52" width="13.8984375" customWidth="1"/>
-    <col min="53" max="53" width="12.5" customWidth="1"/>
-    <col min="54" max="54" width="12.3984375" customWidth="1"/>
-    <col min="55" max="55" width="18.19921875" customWidth="1"/>
-    <col min="56" max="56" width="13.69921875" customWidth="1"/>
-    <col min="57" max="57" width="14" customWidth="1"/>
-    <col min="58" max="58" width="23" customWidth="1"/>
-    <col min="59" max="59" width="15.5" customWidth="1"/>
-    <col min="60" max="60" width="14.296875" customWidth="1"/>
-    <col min="61" max="61" width="14.19921875" customWidth="1"/>
-    <col min="62" max="62" width="12.8984375" customWidth="1"/>
-    <col min="63" max="63" width="22" customWidth="1"/>
-    <col min="64" max="64" width="21" customWidth="1"/>
+    <col min="1" max="1" width="14.5" customWidth="true" style="0"/>
+    <col min="2" max="2" width="11.3984375" customWidth="true" style="0"/>
+    <col min="3" max="3" width="16.5" customWidth="true" style="0"/>
+    <col min="4" max="4" width="12.09765625" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.09765625" customWidth="true" style="0"/>
+    <col min="6" max="6" width="9.8984375" customWidth="true" style="0"/>
+    <col min="7" max="7" width="19.19921875" customWidth="true" style="0"/>
+    <col min="8" max="8" width="22.59765625" customWidth="true" style="0"/>
+    <col min="9" max="9" width="18.3984375" customWidth="true" style="0"/>
+    <col min="10" max="10" width="15.8984375" customWidth="true" style="0"/>
+    <col min="11" max="11" width="14" customWidth="true" style="0"/>
+    <col min="12" max="12" width="13.296875" customWidth="true" style="0"/>
+    <col min="13" max="13" width="13.69921875" customWidth="true" style="0"/>
+    <col min="14" max="14" width="15.796875" customWidth="true" style="0"/>
+    <col min="16" max="16" width="14.69921875" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.5" customWidth="true" style="0"/>
+    <col min="18" max="18" width="16.5" customWidth="true" style="0"/>
+    <col min="19" max="19" width="20.796875" customWidth="true" style="0"/>
+    <col min="20" max="20" width="21.09765625" customWidth="true" style="0"/>
+    <col min="21" max="21" width="24.5" customWidth="true" style="0"/>
+    <col min="22" max="22" width="23.796875" customWidth="true" style="0"/>
+    <col min="23" max="23" width="23.19921875" customWidth="true" style="0"/>
+    <col min="24" max="24" width="23.69921875" customWidth="true" style="0"/>
+    <col min="25" max="25" width="23.69921875" customWidth="true" style="0"/>
+    <col min="26" max="26" width="24.296875" customWidth="true" style="0"/>
+    <col min="27" max="27" width="24.796875" customWidth="true" style="0"/>
+    <col min="28" max="28" width="28.8984375" customWidth="true" style="0"/>
+    <col min="29" max="29" width="30.5" customWidth="true" style="0"/>
+    <col min="30" max="30" width="26.59765625" customWidth="true" style="0"/>
+    <col min="31" max="31" width="26.5" customWidth="true" style="0"/>
+    <col min="32" max="32" width="24.3984375" customWidth="true" style="0"/>
+    <col min="33" max="33" width="23.5" customWidth="true" style="0"/>
+    <col min="34" max="34" width="28.796875" customWidth="true" style="0"/>
+    <col min="35" max="35" width="28.5" customWidth="true" style="0"/>
+    <col min="36" max="36" width="33.796875" customWidth="true" style="0"/>
+    <col min="37" max="37" width="37.59765625" customWidth="true" style="0"/>
+    <col min="38" max="38" width="28.796875" customWidth="true" style="0"/>
+    <col min="39" max="39" width="25.5" customWidth="true" style="0"/>
+    <col min="40" max="40" width="22.3984375" customWidth="true" style="0"/>
+    <col min="41" max="41" width="21.796875" customWidth="true" style="0"/>
+    <col min="42" max="42" width="21.296875" customWidth="true" style="0"/>
+    <col min="43" max="43" width="23.796875" customWidth="true" style="0"/>
+    <col min="44" max="44" width="26.5" customWidth="true" style="0"/>
+    <col min="45" max="45" width="23.5" customWidth="true" style="0"/>
+    <col min="46" max="46" width="25.09765625" customWidth="true" style="0"/>
+    <col min="47" max="47" width="24.8984375" customWidth="true" style="0"/>
+    <col min="48" max="48" width="24.19921875" customWidth="true" style="0"/>
+    <col min="49" max="49" width="23.5" customWidth="true" style="0"/>
+    <col min="50" max="50" width="15.296875" customWidth="true" style="0"/>
+    <col min="51" max="51" width="18.5" customWidth="true" style="0"/>
+    <col min="52" max="52" width="17.796875" customWidth="true" style="0"/>
+    <col min="53" max="53" width="13.8984375" customWidth="true" style="0"/>
+    <col min="54" max="54" width="12.5" customWidth="true" style="0"/>
+    <col min="55" max="55" width="12.3984375" customWidth="true" style="0"/>
+    <col min="56" max="56" width="18.19921875" customWidth="true" style="0"/>
+    <col min="57" max="57" width="13.69921875" customWidth="true" style="0"/>
+    <col min="59" max="59" width="14" customWidth="true" style="0"/>
+    <col min="60" max="60" width="23" customWidth="true" style="0"/>
+    <col min="61" max="61" width="15.5" customWidth="true" style="0"/>
+    <col min="62" max="62" width="14.296875" customWidth="true" style="0"/>
+    <col min="63" max="63" width="14.19921875" customWidth="true" style="0"/>
+    <col min="64" max="64" width="12.8984375" customWidth="true" style="0"/>
+    <col min="65" max="65" width="22" customWidth="true" style="0"/>
+    <col min="66" max="66" width="21" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="15.6">
+    <row r="1" spans="1:66" customHeight="1" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,22 +816,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
       <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
         <v>9</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
@@ -976,28 +975,34 @@
         <v>56</v>
       </c>
       <c r="BF1" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="BG1" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="BH1" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="BI1" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="BJ1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="BK1" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="BL1" t="s">
-        <v>63</v>
+        <v>96</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>95</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:64" ht="14.4">
+    <row r="2" spans="1:66" customHeight="1" ht="14.4">
       <c r="A2">
         <v>1334</v>
       </c>
@@ -1005,199 +1010,209 @@
         <v>1445</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="H2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J2" t="s">
         <v>64</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>65</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>66</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>67</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>68</v>
       </c>
-      <c r="M2" t="s">
+      <c r="P2">
+        <v>5</v>
+      </c>
+      <c r="Q2">
+        <v>8</v>
+      </c>
+      <c r="R2">
+        <v>2</v>
+      </c>
+      <c r="S2" t="s">
         <v>69</v>
       </c>
-      <c r="N2" t="s">
+      <c r="T2" t="s">
         <v>70</v>
       </c>
-      <c r="O2">
-        <v>5</v>
-      </c>
-      <c r="P2">
-        <v>8</v>
-      </c>
-      <c r="Q2">
-        <v>2</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>71</v>
       </c>
-      <c r="S2" t="s">
+      <c r="V2">
+        <v>3800</v>
+      </c>
+      <c r="W2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X2" t="s">
         <v>72</v>
       </c>
-      <c r="T2" t="s">
+      <c r="Y2" t="s">
         <v>73</v>
       </c>
-      <c r="U2">
-        <v>3800</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD2">
+        <v>3500</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF2" t="s">
         <v>72</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AG2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH2" t="s">
         <v>74</v>
       </c>
-      <c r="X2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA2" t="s">
+      <c r="AI2" t="s">
         <v>78</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AJ2" t="s">
         <v>79</v>
       </c>
-      <c r="AC2">
-        <v>3500</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE2" t="s">
+      <c r="AK2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM2">
+        <v>1712345678</v>
+      </c>
+      <c r="AN2">
+        <v>1912345678</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR2">
+        <v>1212</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV2" t="s">
         <v>74</v>
       </c>
-      <c r="AF2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL2">
+      <c r="AW2">
+        <v>1234567890</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY2" s="4">
+        <v>46898</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA2" s="4">
+        <v>45823</v>
+      </c>
+      <c r="BB2" s="4">
+        <v>46246</v>
+      </c>
+      <c r="BC2" s="4">
+        <v>46631</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>88</v>
+      </c>
+      <c r="BE2" s="4">
+        <v>32978</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>74</v>
+      </c>
+      <c r="BH2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BI2">
         <v>1712345678</v>
       </c>
-      <c r="AM2">
+      <c r="BJ2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK2">
         <v>1912345678</v>
       </c>
-      <c r="AN2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AQ2">
-        <v>1212</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AV2">
-        <v>1234567890</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AX2" s="4">
-        <v>46898</v>
-      </c>
-      <c r="AY2" t="s">
+      <c r="BL2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BM2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BN2" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="AZ2" s="4">
-        <v>45823</v>
-      </c>
-      <c r="BA2" s="4">
-        <v>46246</v>
-      </c>
-      <c r="BB2" s="4">
-        <v>46631</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>90</v>
-      </c>
-      <c r="BD2" s="4">
-        <v>32978</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BF2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="BG2">
-        <v>1712345678</v>
-      </c>
-      <c r="BH2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="BI2">
-        <v>1912345678</v>
-      </c>
-      <c r="BJ2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="BK2" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BL2" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AK2" r:id="rId1" xr:uid="{F8BFBEFF-8760-4022-8F8A-E7C19064961C}"/>
-    <hyperlink ref="BK2" r:id="rId2" xr:uid="{480C1799-C1D8-4AD8-8446-91542F36A8F8}"/>
-    <hyperlink ref="BL2" r:id="rId3" xr:uid="{9133AFB1-A375-44E3-B3B6-9AF5432452A8}"/>
+    <hyperlink ref="AL2" r:id="rId_hyperlink_1"/>
+    <hyperlink ref="BN2" r:id="rId_hyperlink_2"/>
+    <hyperlink ref="BM2" r:id="rId_hyperlink_3"/>
   </hyperlinks>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId4ps"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>